--- a/miraen-sentences-v1.xlsx
+++ b/miraen-sentences-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\chunkify_lora\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790F8522-22F2-40BC-9860-87DA87B19213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E348FC8-E096-4869-990A-E9DA80D4AD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="7710" windowWidth="21930" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2445" yWindow="7680" windowWidth="21930" windowHeight="13140" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="프로토타입 요건" sheetId="5" r:id="rId1"/>
